--- a/AAII_Financials/Yearly/ANIX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ANIX_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>ANIX</t>
   </si>
@@ -656,105 +656,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>44865</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44500</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44135</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43769</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43404</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43039</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42674</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42308</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>41943</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41578</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41213</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
+      <c r="D8" s="3">
+        <v>200</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>500</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
       <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>900</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -788,12 +794,15 @@
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N9" s="3">
-        <v>0</v>
-      </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -827,12 +836,15 @@
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="3">
         <v>900</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -848,34 +860,35 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E12" s="3">
         <v>6700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6800</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1600</v>
       </c>
       <c r="J12" s="3">
         <v>1600</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>5</v>
+      <c r="K12" s="3">
+        <v>1600</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>5</v>
@@ -883,12 +896,15 @@
       <c r="M12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O12" s="3">
         <v>2200</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,48 +941,54 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -976,14 +998,14 @@
       <c r="E15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
+      <c r="F15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
         <v>400</v>
-      </c>
-      <c r="H15" s="3">
-        <v>300</v>
       </c>
       <c r="I15" s="3">
         <v>300</v>
@@ -997,15 +1019,18 @@
       <c r="L15" s="3">
         <v>300</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>5</v>
+      <c r="M15" s="3">
+        <v>300</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1018,86 +1043,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E17" s="3">
         <v>13900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5200</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
+      <c r="D18" s="3">
+        <v>-11000</v>
       </c>
       <c r="E18" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-13100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-14300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-4500</v>
       </c>
       <c r="J18" s="3">
         <v>-4500</v>
       </c>
       <c r="K18" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="L18" s="3">
         <v>-900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4300</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1113,26 +1145,27 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>1100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1143,56 +1176,62 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="3">
         <v>-13100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-10100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-13900</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-4100</v>
       </c>
       <c r="J21" s="3">
         <v>-4100</v>
       </c>
       <c r="K21" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3">
         <v>-4200</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1208,11 +1247,11 @@
       <c r="G22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I22" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>500</v>
@@ -1221,56 +1260,62 @@
         <v>500</v>
       </c>
       <c r="L22" s="3">
+        <v>500</v>
+      </c>
+      <c r="M22" s="3">
         <v>1300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1100</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-11800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14200</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-5000</v>
       </c>
       <c r="J23" s="3">
         <v>-5000</v>
       </c>
       <c r="K23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="L23" s="3">
         <v>-1400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4300</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1307,9 +1352,12 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1346,87 +1394,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14200</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-5000</v>
       </c>
       <c r="J26" s="3">
         <v>-5000</v>
       </c>
       <c r="K26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="L26" s="3">
         <v>-1400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4300</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-13600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4300</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1463,9 +1520,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1502,9 +1562,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1541,9 +1604,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1580,27 +1646,30 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>-1100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -1611,56 +1680,62 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-13600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4300</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1697,92 +1772,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-13600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4300</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>44865</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44500</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44135</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43769</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43404</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43039</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42674</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42308</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>41943</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41578</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41213</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1798,8 +1882,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1815,125 +1900,135 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>900</v>
+      </c>
+      <c r="E41" s="3">
         <v>12400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>29100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>300</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E42" s="3">
         <v>17300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2500</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>500</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>5</v>
+      <c r="D43" s="3">
+        <v>300</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1970,23 +2065,26 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="3">
         <v>500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>300</v>
       </c>
       <c r="F45" s="3">
         <v>300</v>
       </c>
       <c r="G45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H45" s="3">
         <v>200</v>
@@ -1998,59 +2096,65 @@
         <v>200</v>
       </c>
       <c r="K45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L45" s="3">
         <v>100</v>
       </c>
       <c r="M45" s="3">
+        <v>100</v>
+      </c>
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E46" s="3">
         <v>30200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>36000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>900</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2082,14 +2186,17 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>4200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4700</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2097,26 +2204,26 @@
         <v>200</v>
       </c>
       <c r="E48" s="3">
+        <v>200</v>
+      </c>
+      <c r="F48" s="3">
         <v>300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>200</v>
-      </c>
-      <c r="H48" s="3">
-        <v>100</v>
       </c>
       <c r="I48" s="3">
         <v>100</v>
       </c>
       <c r="J48" s="3">
+        <v>100</v>
+      </c>
+      <c r="K48" s="3">
         <v>200</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
       <c r="L48" s="3">
         <v>0</v>
       </c>
@@ -2126,9 +2233,12 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2141,33 +2251,36 @@
       <c r="F49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
+      <c r="G49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2700</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2204,9 +2317,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2243,23 +2359,26 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>5</v>
+      <c r="G52" s="3">
+        <v>0</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>5</v>
@@ -2276,15 +2395,18 @@
       <c r="L52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2321,48 +2443,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E54" s="3">
         <v>30400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5700</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2378,8 +2506,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2395,47 +2524,51 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>600</v>
       </c>
       <c r="H57" s="3">
         <v>600</v>
       </c>
       <c r="I57" s="3">
+        <v>600</v>
+      </c>
+      <c r="J57" s="3">
         <v>500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>400</v>
       </c>
       <c r="K57" s="3">
         <v>400</v>
       </c>
       <c r="L57" s="3">
+        <v>400</v>
+      </c>
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2472,9 +2605,12 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2482,38 +2618,41 @@
         <v>1800</v>
       </c>
       <c r="E59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F59" s="3">
         <v>1100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1500</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2521,38 +2660,41 @@
         <v>2000</v>
       </c>
       <c r="E60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1800</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2584,25 +2726,28 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>5500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5000</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E62" s="3">
         <v>200</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>5</v>
+      <c r="F62" s="3">
+        <v>200</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>5</v>
@@ -2610,27 +2755,30 @@
       <c r="H62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>4200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3200</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2667,9 +2815,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2706,9 +2857,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2745,48 +2899,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6900</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2802,8 +2962,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2840,9 +3001,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2879,9 +3043,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2918,9 +3085,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2957,48 +3127,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-228200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-218400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-204800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-191800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-181800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-170200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-156200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-151200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-146100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-144800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-135200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-125100</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3035,9 +3211,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3074,9 +3253,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3113,48 +3295,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E76" s="3">
         <v>29000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>35400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-3300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-1200</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3191,92 +3379,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>44865</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44500</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44135</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43769</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43404</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43039</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42674</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42308</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>41943</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41578</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41213</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-13600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4300</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3292,47 +3489,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>400</v>
       </c>
       <c r="J83" s="3">
         <v>400</v>
       </c>
       <c r="K83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>300</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3369,9 +3570,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3408,9 +3612,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3447,9 +3654,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3486,9 +3696,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3525,48 +3738,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3100</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3582,37 +3801,38 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -3620,9 +3840,12 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3659,9 +3882,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3698,48 +3924,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1500</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-2500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1700</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3755,8 +3987,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3793,9 +4026,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3832,9 +4068,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3871,9 +4110,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3910,48 +4152,54 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
         <v>500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>31600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>7400</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>7300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1000</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3988,46 +4236,52 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>22700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ANIX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ANIX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>ANIX</t>
   </si>
@@ -725,14 +725,14 @@
       <c r="D8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F8" s="3">
         <v>500</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H8" s="3">
         <v>300</v>
@@ -764,26 +764,26 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>200</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
+      <c r="F9" s="3">
+        <v>400</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
+      <c r="H9" s="3">
+        <v>200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>800</v>
+      </c>
+      <c r="J9" s="3">
+        <v>100</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -806,26 +806,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
+      <c r="F10" s="3">
+        <v>100</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="H10" s="3">
+        <v>100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>300</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -950,23 +950,23 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>200</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>600</v>
-      </c>
-      <c r="I14" s="3">
-        <v>1400</v>
       </c>
       <c r="J14" s="3">
         <v>-1500</v>
@@ -992,14 +992,14 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>5</v>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
@@ -1059,16 +1059,16 @@
         <v>13600</v>
       </c>
       <c r="G17" s="3">
-        <v>10000</v>
+        <v>10300</v>
       </c>
       <c r="H17" s="3">
-        <v>12100</v>
+        <v>11700</v>
       </c>
       <c r="I17" s="3">
-        <v>15400</v>
+        <v>14800</v>
       </c>
       <c r="J17" s="3">
-        <v>4900</v>
+        <v>6400</v>
       </c>
       <c r="K17" s="3">
         <v>4800</v>
@@ -1101,16 +1101,16 @@
         <v>-13100</v>
       </c>
       <c r="G18" s="3">
-        <v>-10000</v>
+        <v>-10300</v>
       </c>
       <c r="H18" s="3">
-        <v>-11900</v>
+        <v>-11500</v>
       </c>
       <c r="I18" s="3">
-        <v>-14300</v>
+        <v>-13700</v>
       </c>
       <c r="J18" s="3">
-        <v>-4500</v>
+        <v>-6100</v>
       </c>
       <c r="K18" s="3">
         <v>-4500</v>
@@ -1151,26 +1151,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1193,26 +1193,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-13900</v>
       </c>
       <c r="F21" s="3">
         <v>-13100</v>
       </c>
       <c r="G21" s="3">
-        <v>-10100</v>
+        <v>-10300</v>
       </c>
       <c r="H21" s="3">
-        <v>-11400</v>
+        <v>-11100</v>
       </c>
       <c r="I21" s="3">
-        <v>-13900</v>
+        <v>-13400</v>
       </c>
       <c r="J21" s="3">
-        <v>-4100</v>
+        <v>-5800</v>
       </c>
       <c r="K21" s="3">
         <v>-4100</v>
@@ -1250,8 +1250,8 @@
       <c r="H22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J22" s="3">
         <v>500</v>
@@ -1319,26 +1319,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>-13600</v>
       </c>
       <c r="F27" s="3">
-        <v>-13000</v>
+        <v>-12900</v>
       </c>
       <c r="G27" s="3">
         <v>-10000</v>
       </c>
       <c r="H27" s="3">
-        <v>-11600</v>
+        <v>-11700</v>
       </c>
       <c r="I27" s="3">
         <v>-14000</v>
@@ -1655,26 +1655,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>-14000</v>
       </c>
       <c r="J33" s="3">
-        <v>-7000</v>
+        <v>-5000</v>
       </c>
       <c r="K33" s="3">
         <v>-5000</v>
@@ -1800,7 +1800,7 @@
         <v>-14000</v>
       </c>
       <c r="J35" s="3">
-        <v>-7000</v>
+        <v>-5000</v>
       </c>
       <c r="K35" s="3">
         <v>-5000</v>
@@ -1993,14 +1993,14 @@
       <c r="D43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>5</v>
+      <c r="E43" s="3">
+        <v>0</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G43" s="3">
-        <v>0</v>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H43" s="3">
         <v>100</v>
@@ -2032,26 +2032,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2074,26 +2074,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>200</v>
@@ -2158,26 +2158,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2242,17 +2242,17 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>5</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
@@ -2374,8 +2374,8 @@
       <c r="E52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2582,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -2614,26 +2614,26 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="E59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>900</v>
-      </c>
-      <c r="I59" s="3">
-        <v>700</v>
-      </c>
-      <c r="J59" s="3">
-        <v>400</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>100</v>
@@ -2699,13 +2699,13 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2740,14 +2740,14 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>200</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>5</v>
@@ -2758,8 +2758,8 @@
       <c r="I62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K62" s="3">
         <v>4200</v>
@@ -2909,22 +2909,22 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G66" s="3">
         <v>1200</v>
       </c>
-      <c r="E66" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F66" s="3">
-        <v>800</v>
-      </c>
-      <c r="G66" s="3">
-        <v>700</v>
-      </c>
       <c r="H66" s="3">
-        <v>1100</v>
+        <v>1500</v>
       </c>
       <c r="I66" s="3">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="J66" s="3">
         <v>900</v>
@@ -3454,7 +3454,7 @@
         <v>-14000</v>
       </c>
       <c r="J81" s="3">
-        <v>-7000</v>
+        <v>-5000</v>
       </c>
       <c r="K81" s="3">
         <v>-5000</v>
@@ -3495,26 +3495,26 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>400</v>
@@ -3813,8 +3813,8 @@
       <c r="E91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -4203,26 +4203,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/ANIX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ANIX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
   <si>
     <t>ANIX</t>
   </si>
@@ -656,138 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44865</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44500</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44135</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43769</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43404</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43039</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42674</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42308</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41943</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41578</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41213</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3">
         <v>500</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>900</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3">
         <v>200</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="F9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3">
         <v>400</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="3">
         <v>200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
@@ -797,38 +803,41 @@
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="3">
         <v>100</v>
-      </c>
-      <c r="I10" s="3">
-        <v>300</v>
       </c>
       <c r="J10" s="3">
         <v>300</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
+      <c r="K10" s="3">
+        <v>300</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
@@ -839,12 +848,15 @@
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>900</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,37 +873,38 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E12" s="3">
         <v>4800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6800</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1600</v>
       </c>
       <c r="K12" s="3">
         <v>1600</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>5</v>
+      <c r="L12" s="3">
+        <v>1600</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>5</v>
@@ -899,12 +912,15 @@
       <c r="N12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="3">
         <v>2200</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,9 +960,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -956,39 +975,42 @@
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1005,10 +1027,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>300</v>
       </c>
       <c r="J15" s="3">
         <v>300</v>
@@ -1022,15 +1044,18 @@
       <c r="M15" s="3">
         <v>300</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>5</v>
+      <c r="N15" s="3">
+        <v>300</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E17" s="3">
         <v>11200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5200</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4300</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,8 +1178,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1172,66 +1205,72 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-11000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-10300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-11100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-13400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>-4200</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1253,8 +1292,8 @@
       <c r="I22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J22" s="3">
-        <v>500</v>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>500</v>
@@ -1263,59 +1302,65 @@
         <v>500</v>
       </c>
       <c r="M22" s="3">
+        <v>500</v>
+      </c>
+      <c r="N22" s="3">
         <v>1300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-11800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14200</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-5000</v>
       </c>
       <c r="K23" s="3">
         <v>-5000</v>
       </c>
       <c r="L23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="M23" s="3">
         <v>-1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4300</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1340,8 +1385,8 @@
       <c r="J24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1355,9 +1400,12 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14200</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-5000</v>
       </c>
       <c r="K26" s="3">
         <v>-5000</v>
       </c>
       <c r="L26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="M26" s="3">
         <v>-1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4300</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4300</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,9 +1715,12 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1676,66 +1745,72 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14000</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-5000</v>
       </c>
       <c r="K33" s="3">
         <v>-5000</v>
       </c>
       <c r="L33" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="M33" s="3">
         <v>-1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4300</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14000</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-5000</v>
       </c>
       <c r="K35" s="3">
         <v>-5000</v>
       </c>
       <c r="L35" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="M35" s="3">
         <v>-1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4300</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44865</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44500</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44135</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43769</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43404</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43039</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42674</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42308</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41943</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41578</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41213</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,134 +1986,144 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E41" s="3">
         <v>900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>29100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E42" s="3">
         <v>22900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>17300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2500</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>500</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>5</v>
+      <c r="F43" s="3">
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2053,8 +2148,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2068,9 +2163,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2095,66 +2193,72 @@
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>100</v>
       </c>
       <c r="M45" s="3">
         <v>100</v>
       </c>
       <c r="N45" s="3">
+        <v>100</v>
+      </c>
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E46" s="3">
         <v>25400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>30200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>36000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>900</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2179,8 +2283,8 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2189,14 +2293,17 @@
         <v>0</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>4200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4700</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2207,26 +2314,26 @@
         <v>200</v>
       </c>
       <c r="F48" s="3">
+        <v>200</v>
+      </c>
+      <c r="G48" s="3">
         <v>300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>200</v>
-      </c>
-      <c r="I48" s="3">
-        <v>100</v>
       </c>
       <c r="J48" s="3">
         <v>100</v>
       </c>
       <c r="K48" s="3">
+        <v>100</v>
+      </c>
+      <c r="L48" s="3">
         <v>200</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
       <c r="M48" s="3">
         <v>0</v>
       </c>
@@ -2236,9 +2343,12 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2258,29 +2368,32 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2700</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,9 +2478,12 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2377,11 +2496,11 @@
       <c r="F52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>5</v>
@@ -2398,15 +2517,18 @@
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="N52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E54" s="3">
         <v>25500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5700</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,68 +2654,72 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>600</v>
       </c>
       <c r="I57" s="3">
         <v>600</v>
       </c>
       <c r="J57" s="3">
+        <v>600</v>
+      </c>
+      <c r="K57" s="3">
         <v>500</v>
-      </c>
-      <c r="K57" s="3">
-        <v>400</v>
       </c>
       <c r="L57" s="3">
         <v>400</v>
       </c>
       <c r="M57" s="3">
+        <v>400</v>
+      </c>
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>100</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>100</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -2608,9 +2741,12 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2635,80 +2771,86 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1500</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E60" s="3">
         <v>2000</v>
       </c>
       <c r="F60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G60" s="3">
         <v>1300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1800</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>200</v>
+      </c>
+      <c r="E61" s="3">
         <v>100</v>
-      </c>
-      <c r="E61" s="3">
-        <v>200</v>
       </c>
       <c r="F61" s="3">
         <v>200</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2729,14 +2871,17 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>5500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2761,24 +2906,27 @@
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3">
         <v>4200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2200</v>
+        <v>2700</v>
       </c>
       <c r="E66" s="3">
         <v>2200</v>
       </c>
       <c r="F66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G66" s="3">
         <v>1500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6900</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-240800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-228200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-218400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-204800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-191800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-181800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-170200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-156200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-151200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-146100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-144800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-135200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-125100</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E76" s="3">
         <v>24300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>29000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>35400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-3300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-1200</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44865</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44500</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44135</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43769</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43404</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43039</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42674</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42308</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41943</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41578</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41213</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14000</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-5000</v>
       </c>
       <c r="K81" s="3">
         <v>-5000</v>
       </c>
       <c r="L81" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="M81" s="3">
         <v>-1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4300</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,8 +3687,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3502,13 +3700,13 @@
         <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
@@ -3517,23 +3715,26 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>400</v>
-      </c>
-      <c r="L83" s="3">
-        <v>300</v>
       </c>
       <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>300</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3100</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,8 +4021,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3816,26 +4036,26 @@
       <c r="F91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -3843,9 +4063,12 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1500</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-2500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1700</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,8 +4220,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4029,9 +4262,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,51 +4397,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>31600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>7400</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>7300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4224,8 +4472,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4239,49 +4487,55 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>22700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-400</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ANIX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ANIX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
   <si>
     <t>ANIX</t>
   </si>
@@ -656,147 +656,153 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E7" s="2">
         <v>45596</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44865</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44500</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44135</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43769</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43404</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43039</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42674</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42308</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41943</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41578</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41213</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3">
         <v>500</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>900</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3">
         <v>200</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="G9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="3">
         <v>400</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="3">
         <v>200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
@@ -806,41 +812,44 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3">
         <v>100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>300</v>
       </c>
       <c r="K10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
+      <c r="L10" s="3">
+        <v>300</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
@@ -851,12 +860,15 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3">
         <v>900</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -874,40 +886,41 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E12" s="3">
         <v>6400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6800</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1600</v>
       </c>
       <c r="L12" s="3">
         <v>1600</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>5</v>
+      <c r="M12" s="3">
+        <v>1600</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>5</v>
@@ -915,12 +928,15 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3">
         <v>2200</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,9 +979,12 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -978,39 +997,42 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1030,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>400</v>
-      </c>
-      <c r="J15" s="3">
-        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>300</v>
@@ -1047,15 +1069,18 @@
       <c r="N15" s="3">
         <v>300</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>5</v>
+      <c r="O15" s="3">
+        <v>300</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E17" s="3">
         <v>13800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5200</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-11000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-10300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,8 +1211,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1208,69 +1241,75 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-13800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-13100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-10300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-11100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-13400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1295,8 +1334,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>500</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>500</v>
@@ -1305,62 +1344,68 @@
         <v>500</v>
       </c>
       <c r="N22" s="3">
+        <v>500</v>
+      </c>
+      <c r="O22" s="3">
         <v>1300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1100</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-11800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14200</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-5000</v>
       </c>
       <c r="L23" s="3">
         <v>-5000</v>
       </c>
       <c r="M23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="N23" s="3">
         <v>-1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1388,8 +1433,8 @@
       <c r="K24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1403,9 +1448,12 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14200</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-5000</v>
       </c>
       <c r="L26" s="3">
         <v>-5000</v>
       </c>
       <c r="M26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="N26" s="3">
         <v>-1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,9 +1784,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1748,69 +1817,75 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14000</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-5000</v>
       </c>
       <c r="L33" s="3">
         <v>-5000</v>
       </c>
       <c r="M33" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="N33" s="3">
         <v>-1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14000</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-5000</v>
       </c>
       <c r="L35" s="3">
         <v>-5000</v>
       </c>
       <c r="M35" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="N35" s="3">
         <v>-1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E38" s="2">
         <v>45596</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44865</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44500</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44135</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43769</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43404</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43039</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42674</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42308</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41943</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41578</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41213</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,143 +2072,153 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>29100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>300</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E42" s="3">
         <v>18700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>22900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>17300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2500</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>500</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>5</v>
+      <c r="G43" s="3">
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2151,8 +2246,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2166,9 +2261,12 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2196,69 +2294,75 @@
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>200</v>
-      </c>
-      <c r="M45" s="3">
-        <v>100</v>
       </c>
       <c r="N45" s="3">
         <v>100</v>
       </c>
       <c r="O45" s="3">
+        <v>100</v>
+      </c>
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E46" s="3">
         <v>21400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>30200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>36000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>900</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2286,8 +2390,8 @@
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2296,14 +2400,17 @@
         <v>0</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>4200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4700</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2317,26 +2424,26 @@
         <v>200</v>
       </c>
       <c r="G48" s="3">
+        <v>200</v>
+      </c>
+      <c r="H48" s="3">
         <v>300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>200</v>
-      </c>
-      <c r="J48" s="3">
-        <v>100</v>
       </c>
       <c r="K48" s="3">
         <v>100</v>
       </c>
       <c r="L48" s="3">
+        <v>100</v>
+      </c>
+      <c r="M48" s="3">
         <v>200</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
       <c r="N48" s="3">
         <v>0</v>
       </c>
@@ -2346,9 +2453,12 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2371,29 +2481,32 @@
         <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2700</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,9 +2597,12 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2499,11 +2618,11 @@
       <c r="G52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
@@ -2520,15 +2639,18 @@
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E54" s="3">
         <v>21600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5700</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,53 +2784,57 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200</v>
+      </c>
+      <c r="E57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
-      </c>
-      <c r="I57" s="3">
-        <v>600</v>
       </c>
       <c r="J57" s="3">
         <v>600</v>
       </c>
       <c r="K57" s="3">
+        <v>600</v>
+      </c>
+      <c r="L57" s="3">
         <v>500</v>
-      </c>
-      <c r="L57" s="3">
-        <v>400</v>
       </c>
       <c r="M57" s="3">
         <v>400</v>
       </c>
       <c r="N57" s="3">
+        <v>400</v>
+      </c>
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>300</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2709,20 +2842,20 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>100</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>100</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -2744,9 +2877,12 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2774,69 +2910,75 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1500</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2500</v>
-      </c>
-      <c r="E60" s="3">
-        <v>2000</v>
       </c>
       <c r="F60" s="3">
         <v>2000</v>
       </c>
       <c r="G60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H60" s="3">
         <v>1300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1800</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2844,16 +2986,16 @@
         <v>200</v>
       </c>
       <c r="E61" s="3">
+        <v>200</v>
+      </c>
+      <c r="F61" s="3">
         <v>100</v>
-      </c>
-      <c r="F61" s="3">
-        <v>200</v>
       </c>
       <c r="G61" s="3">
         <v>200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2874,14 +3016,17 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>5500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2909,24 +3054,27 @@
       <c r="K62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3">
         <v>4200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3200</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2700</v>
-      </c>
-      <c r="E66" s="3">
-        <v>2200</v>
       </c>
       <c r="F66" s="3">
         <v>2200</v>
       </c>
       <c r="G66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H66" s="3">
         <v>1500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6900</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-251700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-240800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-228200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-218400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-204800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-191800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-181800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-170200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-156200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-151200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-146100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-144800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-135200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-125100</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E76" s="3">
         <v>20000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>29000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>35400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-3300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E80" s="2">
         <v>45596</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44865</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44500</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44135</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43769</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43404</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43039</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42674</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42308</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41943</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41578</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41213</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14000</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-5000</v>
       </c>
       <c r="L81" s="3">
         <v>-5000</v>
       </c>
       <c r="M81" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="N81" s="3">
         <v>-1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,8 +3885,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3703,13 +3901,13 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -3718,23 +3916,26 @@
         <v>0</v>
       </c>
       <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>400</v>
-      </c>
-      <c r="M83" s="3">
-        <v>300</v>
       </c>
       <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>300</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,8 +4241,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4039,26 +4259,26 @@
       <c r="G91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -4066,9 +4286,12 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E94" s="3">
         <v>4300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1500</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-2500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1700</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,8 +4453,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4265,9 +4498,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,54 +4642,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E100" s="3">
         <v>3400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>31600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7400</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>7300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4475,8 +4723,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4490,52 +4738,58 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-16800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>22700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-400</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
